--- a/cleaned_what_a_waste_data.xlsx
+++ b/cleaned_what_a_waste_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6197,40 +6197,42 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HIC</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>LMIC</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>70655628147.89999</v>
+      </c>
       <c r="E126" t="n">
-        <v>23370002</v>
+        <v>61894186</v>
       </c>
       <c r="F126" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G126" t="n">
-        <v>11579543</v>
+        <v>14800000</v>
       </c>
       <c r="H126" t="n">
-        <v>1.357499898479502</v>
+        <v>0.6551171899324995</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1741</v>
+        <v>0.37</v>
       </c>
       <c r="J126" t="n">
-        <v>0.3974</v>
+        <v>0.11</v>
       </c>
       <c r="K126" t="n">
-        <v>0.2586</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6241,42 +6243,42 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>E. Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>UMIC</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>70655628147.89999</v>
+        <v>515906283941</v>
       </c>
       <c r="E127" t="n">
-        <v>61894186</v>
+        <v>71715662</v>
       </c>
       <c r="F127" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G127" t="n">
-        <v>14800000</v>
+        <v>26950000</v>
       </c>
       <c r="H127" t="n">
-        <v>0.6551171899324995</v>
+        <v>1.029560550362851</v>
       </c>
       <c r="I127" t="n">
-        <v>0.37</v>
+        <v>0.64</v>
       </c>
       <c r="J127" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="K127" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1762</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -6287,7 +6289,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6297,32 +6299,32 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>LMIC</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>515906283941</v>
+        <v>3624889673</v>
       </c>
       <c r="E128" t="n">
-        <v>71715662</v>
+        <v>1338533</v>
       </c>
       <c r="F128" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G128" t="n">
-        <v>26950000</v>
+        <v>240276.043231</v>
       </c>
       <c r="H128" t="n">
-        <v>1.029560550362851</v>
+        <v>0.4918</v>
       </c>
       <c r="I128" t="n">
-        <v>0.64</v>
+        <v>0.5857</v>
       </c>
       <c r="J128" t="n">
-        <v>0.08</v>
+        <v>0.1301</v>
       </c>
       <c r="K128" t="n">
-        <v>0.1762</v>
+        <v>0.0973</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -6333,42 +6335,42 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>LIC</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3624889673</v>
+        <v>9171261838</v>
       </c>
       <c r="E129" t="n">
-        <v>1338533</v>
+        <v>9196283</v>
       </c>
       <c r="F129" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G129" t="n">
-        <v>240276.043231</v>
+        <v>348000</v>
       </c>
       <c r="H129" t="n">
-        <v>0.4918</v>
+        <v>0.1036750019039482</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5857</v>
+        <v>0.38</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1301</v>
+        <v>0.04</v>
       </c>
       <c r="K129" t="n">
-        <v>0.0973</v>
+        <v>0.1</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6379,42 +6381,42 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>E. Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>UMIC</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9171261838</v>
+        <v>518228029</v>
       </c>
       <c r="E130" t="n">
-        <v>9196283</v>
+        <v>105711</v>
       </c>
       <c r="F130" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G130" t="n">
-        <v>348000</v>
+        <v>9476</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1036750019039482</v>
+        <v>0.2455907505899711</v>
       </c>
       <c r="I130" t="n">
-        <v>0.38</v>
+        <v>0.3998</v>
       </c>
       <c r="J130" t="n">
-        <v>0.04</v>
+        <v>0.204</v>
       </c>
       <c r="K130" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6425,42 +6427,42 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>L. Amer. &amp; the Caribbean</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>HIC</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>518228029</v>
+        <v>24177305760</v>
       </c>
       <c r="E131" t="n">
-        <v>105711</v>
+        <v>1483702</v>
       </c>
       <c r="F131" t="n">
         <v>2021</v>
       </c>
       <c r="G131" t="n">
-        <v>9476</v>
+        <v>780000</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2455907505899711</v>
+        <v>1.440306949353619</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3998</v>
+        <v>0.206</v>
       </c>
       <c r="J131" t="n">
-        <v>0.204</v>
+        <v>0.1796</v>
       </c>
       <c r="K131" t="n">
-        <v>0.105</v>
+        <v>0.1284</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6471,42 +6473,42 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Mid. East &amp; N. Africa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>LMIC</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>24177305760</v>
+        <v>42491780918</v>
       </c>
       <c r="E132" t="n">
-        <v>1483702</v>
+        <v>11928934</v>
       </c>
       <c r="F132" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G132" t="n">
-        <v>780000</v>
+        <v>2810000</v>
       </c>
       <c r="H132" t="n">
-        <v>1.440306949353619</v>
+        <v>0.6453745269264044</v>
       </c>
       <c r="I132" t="n">
-        <v>0.206</v>
+        <v>0.632</v>
       </c>
       <c r="J132" t="n">
-        <v>0.1796</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1284</v>
+        <v>0.094</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6517,42 +6519,42 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Eur. &amp; Cent. Asia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>UMIC</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>42491780918</v>
+        <v>907118434654</v>
       </c>
       <c r="E133" t="n">
-        <v>11928934</v>
+        <v>86947617</v>
       </c>
       <c r="F133" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="G133" t="n">
-        <v>2810000</v>
+        <v>30283757</v>
       </c>
       <c r="H133" t="n">
-        <v>0.6453745269264044</v>
+        <v>0.954243487320348</v>
       </c>
       <c r="I133" t="n">
-        <v>0.632</v>
+        <v>0.5554</v>
       </c>
       <c r="J133" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K133" t="n">
-        <v>0.094</v>
+        <v>0.0586</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6563,12 +6565,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>E. Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6577,28 +6579,28 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>907118434654</v>
+        <v>54129199</v>
       </c>
       <c r="E134" t="n">
-        <v>86947617</v>
+        <v>10670</v>
       </c>
       <c r="F134" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="G134" t="n">
-        <v>30283757</v>
+        <v>1642.6</v>
       </c>
       <c r="H134" t="n">
-        <v>0.954243487320348</v>
+        <v>0.4217688821558332</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5554</v>
+        <v>0.42</v>
       </c>
       <c r="J134" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="K134" t="n">
-        <v>0.0586</v>
+        <v>0.146</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6609,42 +6611,42 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>LIC</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>54129199</v>
+        <v>27871725241.47</v>
       </c>
       <c r="E135" t="n">
-        <v>10670</v>
+        <v>46644329</v>
       </c>
       <c r="F135" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G135" t="n">
-        <v>1642.6</v>
+        <v>10554334</v>
       </c>
       <c r="H135" t="n">
-        <v>0.4217688821558332</v>
+        <v>0.6199249767753354</v>
       </c>
       <c r="I135" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="J135" t="n">
-        <v>0.102</v>
+        <v>0.053</v>
       </c>
       <c r="K135" t="n">
-        <v>0.146</v>
+        <v>0.016</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6655,42 +6657,42 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Eur. &amp; Cent. Asia</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>UMIC</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>27871725241.47</v>
+        <v>181221517869</v>
       </c>
       <c r="E136" t="n">
-        <v>46644329</v>
+        <v>38024411</v>
       </c>
       <c r="F136" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G136" t="n">
-        <v>10554334</v>
+        <v>9349117.905999999</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6199249767753354</v>
+        <v>0.6736204713407388</v>
       </c>
       <c r="I136" t="n">
-        <v>0.73</v>
+        <v>0.44</v>
       </c>
       <c r="J136" t="n">
-        <v>0.053</v>
+        <v>0.13</v>
       </c>
       <c r="K136" t="n">
-        <v>0.016</v>
+        <v>0.11</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -6701,42 +6703,42 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Mid. East &amp; N. Africa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>HIC</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>181221517869</v>
+        <v>502731935194</v>
       </c>
       <c r="E137" t="n">
-        <v>38024411</v>
+        <v>10039142</v>
       </c>
       <c r="F137" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G137" t="n">
-        <v>9349117.905999999</v>
+        <v>4617980</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6736204713407388</v>
+        <v>1.260267062663323</v>
       </c>
       <c r="I137" t="n">
-        <v>0.44</v>
+        <v>0.276200008392333</v>
       </c>
       <c r="J137" t="n">
-        <v>0.13</v>
+        <v>0.261200008392333</v>
       </c>
       <c r="K137" t="n">
-        <v>0.11</v>
+        <v>0.249599990844727</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6747,12 +6749,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>N. Amer.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6761,28 +6763,28 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>502731935194</v>
+        <v>20656516000000</v>
       </c>
       <c r="E138" t="n">
-        <v>10039142</v>
+        <v>333675290</v>
       </c>
       <c r="F138" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="G138" t="n">
-        <v>4617980</v>
+        <v>265260817.976</v>
       </c>
       <c r="H138" t="n">
-        <v>1.260267062663323</v>
+        <v>2.177991564965851</v>
       </c>
       <c r="I138" t="n">
-        <v>0.276200008392333</v>
+        <v>0.216</v>
       </c>
       <c r="J138" t="n">
-        <v>0.261200008392333</v>
+        <v>0.231</v>
       </c>
       <c r="K138" t="n">
-        <v>0.249599990844727</v>
+        <v>0.122</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6793,12 +6795,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>N. Amer.</t>
+          <t>L. Amer. &amp; the Caribbean</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6807,28 +6809,28 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>20656516000000</v>
+        <v>60739084241</v>
       </c>
       <c r="E139" t="n">
-        <v>333675290</v>
+        <v>3400245</v>
       </c>
       <c r="F139" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="G139" t="n">
-        <v>265260817.976</v>
+        <v>1250583.44</v>
       </c>
       <c r="H139" t="n">
-        <v>2.177991564965851</v>
+        <v>1.007649742886174</v>
       </c>
       <c r="I139" t="n">
-        <v>0.216</v>
+        <v>0.402</v>
       </c>
       <c r="J139" t="n">
-        <v>0.231</v>
+        <v>0.138</v>
       </c>
       <c r="K139" t="n">
-        <v>0.122</v>
+        <v>0.173</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6839,42 +6841,42 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Eur. &amp; Cent. Asia</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>LMIC</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>60739084241</v>
+        <v>90095926567</v>
       </c>
       <c r="E140" t="n">
-        <v>3400245</v>
+        <v>34583751</v>
       </c>
       <c r="F140" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G140" t="n">
-        <v>1250583.44</v>
+        <v>6816840.5</v>
       </c>
       <c r="H140" t="n">
-        <v>1.007649742886174</v>
+        <v>0.5400303553673445</v>
       </c>
       <c r="I140" t="n">
-        <v>0.402</v>
+        <v>0.28</v>
       </c>
       <c r="J140" t="n">
-        <v>0.138</v>
+        <v>0.03</v>
       </c>
       <c r="K140" t="n">
-        <v>0.173</v>
+        <v>0.08</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -6885,12 +6887,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>E. Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6899,28 +6901,28 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>90095926567</v>
+        <v>936526267.62</v>
       </c>
       <c r="E141" t="n">
-        <v>34583751</v>
+        <v>288628</v>
       </c>
       <c r="F141" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="G141" t="n">
-        <v>6816840.5</v>
+        <v>41610</v>
       </c>
       <c r="H141" t="n">
-        <v>0.5400303553673445</v>
+        <v>0.3949720747813795</v>
       </c>
       <c r="I141" t="n">
-        <v>0.28</v>
+        <v>0.3721</v>
       </c>
       <c r="J141" t="n">
-        <v>0.03</v>
+        <v>0.0427</v>
       </c>
       <c r="K141" t="n">
-        <v>0.08</v>
+        <v>0.1033</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -6931,7 +6933,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6945,28 +6947,28 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>936526267.62</v>
+        <v>239258328381.74</v>
       </c>
       <c r="E142" t="n">
-        <v>288628</v>
+        <v>92252737</v>
       </c>
       <c r="F142" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="G142" t="n">
-        <v>41610</v>
+        <v>19000000</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3949720747813795</v>
+        <v>0.5642628740711286</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3721</v>
+        <v>0.55</v>
       </c>
       <c r="J142" t="n">
-        <v>0.0427</v>
+        <v>0.05</v>
       </c>
       <c r="K142" t="n">
-        <v>0.1033</v>
+        <v>0.1</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -6977,7 +6979,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Venezuela, RB</t>
+          <t>Virgin Islands (US)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6987,46 +6989,48 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UMC (2019)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>HIC</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>4223000000</v>
+      </c>
       <c r="E143" t="n">
-        <v>28587753</v>
+        <v>105917</v>
       </c>
       <c r="F143" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="G143" t="n">
-        <v>8251445.5</v>
+        <v>146500</v>
       </c>
       <c r="H143" t="n">
-        <v>0.79078268236052</v>
+        <v>3.789475372354756</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>0.089</v>
       </c>
       <c r="J143" t="n">
-        <v>0.2</v>
+        <v>0.185</v>
       </c>
       <c r="K143" t="n">
-        <v>0.1</v>
+        <v>0.136</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Yemen, Rep.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>Mid. East &amp; N. Africa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7035,74 +7039,74 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>239258328381.74</v>
+        <v>31317825274.15</v>
       </c>
       <c r="E144" t="n">
-        <v>92252737</v>
+        <v>31624406</v>
       </c>
       <c r="F144" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G144" t="n">
-        <v>19000000</v>
+        <v>4409561</v>
       </c>
       <c r="H144" t="n">
-        <v>0.5642628740711286</v>
+        <v>0.3820147338449896</v>
       </c>
       <c r="I144" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="J144" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K144" t="n">
         <v>0.1</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Virgin Islands (US)</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>LMIC</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4223000000</v>
+        <v>29163782140.49</v>
       </c>
       <c r="E145" t="n">
-        <v>105917</v>
+        <v>19875494</v>
       </c>
       <c r="F145" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="G145" t="n">
-        <v>146500</v>
+        <v>4352733.186</v>
       </c>
       <c r="H145" t="n">
-        <v>3.789475372354756</v>
+        <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>0.089</v>
+        <v>0.51</v>
       </c>
       <c r="J145" t="n">
-        <v>0.185</v>
+        <v>0.06</v>
       </c>
       <c r="K145" t="n">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7113,12 +7117,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Yemen, Rep.</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7127,122 +7131,30 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>31317825274.15</v>
+        <v>26868564055</v>
       </c>
       <c r="E146" t="n">
-        <v>31624406</v>
+        <v>15394209</v>
       </c>
       <c r="F146" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="G146" t="n">
-        <v>4409561</v>
+        <v>2500000</v>
       </c>
       <c r="H146" t="n">
-        <v>0.3820147338449896</v>
+        <v>0.4449280290070864</v>
       </c>
       <c r="I146" t="n">
-        <v>0.65</v>
+        <v>0.44688</v>
       </c>
       <c r="J146" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16165</v>
       </c>
       <c r="K146" t="n">
-        <v>0.1</v>
+        <v>0.15361</v>
       </c>
       <c r="L146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>LMIC</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>29163782140.49</v>
-      </c>
-      <c r="E147" t="n">
-        <v>19875494</v>
-      </c>
-      <c r="F147" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G147" t="n">
-        <v>4352733.186</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>LMIC</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>26868564055</v>
-      </c>
-      <c r="E148" t="n">
-        <v>15394209</v>
-      </c>
-      <c r="F148" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G148" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0.4449280290070864</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0.44688</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0.16165</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.15361</v>
-      </c>
-      <c r="L148" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/cleaned_what_a_waste_data.xlsx
+++ b/cleaned_what_a_waste_data.xlsx
@@ -498,12 +498,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -544,12 +544,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -590,12 +590,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -636,12 +636,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -728,12 +728,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -774,12 +774,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -820,12 +820,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -866,12 +866,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -958,12 +958,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N. Amer.</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>S. Asia</t>
+          <t>South Asia</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>low-income country</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UMIC</t>
+          <t>upper-middle-income country</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>N. Amer.</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eur. &amp; Cent. Asia</t>
+          <t>Europe and Central Asia</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>E. Asia &amp; Pacific</t>
+          <t>East Asia and Pacific</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>L. Amer. &amp; the Caribbean</t>
+          <t>Latin America and Caribbean</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HIC</t>
+          <t>high-income country</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mid. East &amp; N. Africa</t>
+          <t>Middle East and North Africa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LMIC</t>
+          <t>lower-middle-income country</t>
         </is>
       </c>
       <c r="D146" t="n">
